--- a/examples/EXCEL/GameItemTable.xlsx
+++ b/examples/EXCEL/GameItemTable.xlsx
@@ -4,29 +4,38 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38370" windowHeight="6405"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38370" windowHeight="6405" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="GameItem" sheetId="1" r:id="rId1"/>
-    <sheet name="GameItemTypeTable" sheetId="2" r:id="rId2"/>
+    <sheet name="GameItemTypeDef" sheetId="1" r:id="rId1"/>
+    <sheet name="GameItem" sheetId="2" r:id="rId2"/>
     <sheet name="_DropDown" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="27">
   <si>
+    <t>itemType</t>
+  </si>
+  <si>
+    <t>typeName</t>
+  </si>
+  <si>
+    <t>isTradable</t>
+  </si>
+  <si>
+    <t>iconPath</t>
+  </si>
+  <si>
     <t>itemId</t>
   </si>
   <si>
     <t>name</t>
   </si>
   <si>
-    <t>itemType</t>
-  </si>
-  <si>
     <t>rarity</t>
   </si>
   <si>
@@ -39,59 +48,50 @@
     <t>descriptions</t>
   </si>
   <si>
-    <t>typeName</t>
-  </si>
-  <si>
-    <t>isTradable</t>
-  </si>
-  <si>
-    <t>iconPath</t>
+    <t>ItemType</t>
   </si>
   <si>
     <t>GradeType</t>
   </si>
   <si>
-    <t>ItemType</t>
+    <t>ItemType_NONE</t>
   </si>
   <si>
     <t>GradeType_NONE</t>
   </si>
   <si>
-    <t>ItemType_NONE</t>
+    <t>ItemType_EQUIPMENT</t>
   </si>
   <si>
     <t>GradeType_NORMAL</t>
   </si>
   <si>
-    <t>ItemType_EQUIPMENT</t>
+    <t>ItemType_CONSUMABLE</t>
   </si>
   <si>
     <t>GradeType_SUPERIOR</t>
   </si>
   <si>
-    <t>ItemType_CONSUMABLE</t>
+    <t>ItemType_MATERIAL</t>
   </si>
   <si>
     <t>GradeType_RARE</t>
   </si>
   <si>
-    <t>ItemType_MATERIAL</t>
+    <t>ItemType_QUEST</t>
   </si>
   <si>
     <t>GradeType_EPIC</t>
   </si>
   <si>
-    <t>ItemType_QUEST</t>
-  </si>
-  <si>
     <t>GradeType_LEGENDARY</t>
   </si>
   <si>
-    <t>Newbie</t>
+    <t>D:\icon\icon.icon</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>D:\icon\icon.icon</t>
+    <t>장비</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -457,90 +457,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="21.75" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="18.625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2">
-        <v>34</v>
-      </c>
-      <c r="F2">
-        <v>100</v>
-      </c>
-      <c r="G2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="잘못된 참조" error="GameItemTypeTable 시트의 값을 선택하세요.">
-          <x14:formula1>
-            <xm:f>OFFSET(GameItemTypeTable!$A$2,0,0,MAX(1,COUNTA(GameItemTypeTable!$A$2:$A$21)),1)</xm:f>
-          </x14:formula1>
-          <xm:sqref>C2:C10000</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="잘못된 값" error="정의된 Enum 값을 선택하세요. (GradeType)">
-          <x14:formula1>
-            <xm:f>_DropDown!$A$2:$A$7</xm:f>
-          </x14:formula1>
-          <xm:sqref>D2:D10000</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -551,30 +467,104 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="D1" s="2" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C2" t="b">
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="잘못된 값" error="정의된 Enum 값을 선택하세요. (ItemType)">
+          <x14:formula1>
+            <xm:f>_DropDown!$A$2:$A$6</xm:f>
+          </x14:formula1>
+          <xm:sqref>A2:A10000</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>100</v>
+      </c>
+      <c r="G2" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -583,12 +573,18 @@
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="잘못된 값" error="정의된 Enum 값을 선택하세요. (ItemType)">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="잘못된 참조" error="GameItemTypeDef 시트의 값을 선택하세요.">
           <x14:formula1>
-            <xm:f>_DropDown!$B$2:$B$6</xm:f>
+            <xm:f>OFFSET(GameItemTypeDef!$A$2,0,0,MAX(1,COUNTA(GameItemTypeDef!$A$2:$A$21)),1)</xm:f>
           </x14:formula1>
-          <xm:sqref>A2:A10000</xm:sqref>
+          <xm:sqref>C2:C10000</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="잘못된 값" error="정의된 Enum 값을 선택하세요. (GradeType)">
+          <x14:formula1>
+            <xm:f>_DropDown!$B$2:$B$7</xm:f>
+          </x14:formula1>
+          <xm:sqref>D2:D10000</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -653,7 +649,7 @@
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="B7" t="s">
         <v>22</v>
       </c>
     </row>

--- a/examples/EXCEL/GameItemTable.xlsx
+++ b/examples/EXCEL/GameItemTable.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="29">
   <si>
     <t>itemType</t>
   </si>
@@ -100,6 +100,14 @@
   </si>
   <si>
     <t>뉴비가 쓰는 검이다</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>뉴비의 단검</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>뉴비가 쓰는 단검이다</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -514,7 +522,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="6" width="12" customWidth="1"/>
@@ -565,6 +573,29 @@
       </c>
       <c r="G2" t="s">
         <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>100</v>
+      </c>
+      <c r="G3" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
